--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132670661</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132670661</v>
       </c>
       <c r="B2" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132670661</v>
       </c>
       <c r="B2" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132670661</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132670661</v>
       </c>
       <c r="B2" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132670661</v>
       </c>
       <c r="B2" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 57452-2025 artfynd.xlsx
+++ b/artfynd/A 57452-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132670661</v>
+        <v>132670534</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575844</v>
+        <v>575884</v>
       </c>
       <c r="R2" t="n">
-        <v>6410213</v>
+        <v>6410198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,6 +778,324 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132670563</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 57452, Nyhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>575862</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6410233</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132670661</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 57452, Nyhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575844</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6410213</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132670585</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 57452, Nyhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575862</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6410233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
